--- a/artfynd/A 25467-2026 artfynd.xlsx
+++ b/artfynd/A 25467-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122595851</v>
+        <v>122595850</v>
       </c>
       <c r="B2" t="n">
-        <v>97319</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>795508</v>
+        <v>795512</v>
       </c>
       <c r="R2" t="n">
-        <v>7439608</v>
+        <v>7439816</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -774,22 +769,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122595853</v>
+        <v>122595849</v>
       </c>
       <c r="B3" t="n">
-        <v>97319</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>1365</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>795449</v>
+        <v>795510</v>
       </c>
       <c r="R3" t="n">
-        <v>7439534</v>
+        <v>7439841</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,7 +870,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -890,12 +880,7 @@
         <v>122595852</v>
       </c>
       <c r="B4" t="n">
-        <v>94390</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95962</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,44 +971,39 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122595850</v>
+        <v>122595851</v>
       </c>
       <c r="B5" t="n">
-        <v>82553</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>795512</v>
+        <v>795508</v>
       </c>
       <c r="R5" t="n">
-        <v>7439816</v>
+        <v>7439608</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,10 +1072,111 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122595853</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nordlandet, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>795449</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7439534</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Håkan Tyrén</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25467-2026 artfynd.xlsx
+++ b/artfynd/A 25467-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595850</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595849</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595852</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595851</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,8 +1202,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595853</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>